--- a/plantillas/104.xlsx
+++ b/plantillas/104.xlsx
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/104.xlsx
+++ b/plantillas/104.xlsx
@@ -28,7 +28,7 @@
     <definedName name="MARCA_14">Listas!$Q$2:$Q$4</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$16</definedName>
     <definedName name="MARCA_16">Listas!$S$2:$S$16</definedName>
-    <definedName name="MARCA_17">Listas!$T$2:$T$13</definedName>
+    <definedName name="MARCA_17">Listas!$T$2:$T$16</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$2</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$2</definedName>
     <definedName name="MARCA_20">Listas!$W$2:$W$2</definedName>
@@ -638,11 +638,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B3,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B3,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B3,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B3,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -662,11 +662,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B4,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B4,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B4,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B4,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -686,11 +686,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B5,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B5,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B5,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B5,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -710,11 +710,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B6,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B6,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B6,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B6,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -729,11 +729,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B7,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B7,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B7,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B7,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -748,11 +748,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B8,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B8,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B8,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B8,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -767,11 +767,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B9,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B9,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B9,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B9,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -786,11 +786,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B10,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B10,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B10,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B10,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -805,11 +805,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B11,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B11,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B11,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B11,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -824,11 +824,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B12,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B12,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B12,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B12,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -843,11 +843,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B13,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B13,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B13,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B13,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -862,11 +862,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B14,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B14,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B14,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B14,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -881,11 +881,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B15,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B15,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B15,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B15,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -900,11 +900,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B16,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B16,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B16,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B16,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -919,11 +919,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B17,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B17,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B17,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B17,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -938,11 +938,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B18,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B18,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B18,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B18,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -957,11 +957,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B19,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B19,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B19,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B19,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -976,11 +976,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B20,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B20,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B20,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B20,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -995,11 +995,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B21,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B21,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B21,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B21,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1014,11 +1014,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B22,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B22,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B22,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B22,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1033,11 +1033,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B23,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B23,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B23,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B23,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1052,11 +1052,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B24,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B24,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B24,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B24,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1071,11 +1071,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B25,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B25,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B25,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B25,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1090,11 +1090,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B26,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B26,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B26,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B26,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1109,11 +1109,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B27,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B27,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B27,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B27,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1128,11 +1128,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B28,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B28,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B28,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B28,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1147,11 +1147,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B29,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B29,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B29,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B29,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1166,11 +1166,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B30,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B30,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B30,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B30,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1185,11 +1185,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B31,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B31,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B31,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B31,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1204,11 +1204,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B32,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B32,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B32,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B32,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1223,11 +1223,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B33,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B33,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B33,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B33,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1242,11 +1242,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B34,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B34,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B34,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B34,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1261,11 +1261,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B35,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B35,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B35,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B35,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1280,11 +1280,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B36,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B36,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B36,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B36,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1299,11 +1299,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B37,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B37,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B37,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B37,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1318,11 +1318,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B38,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B38,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B38,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B38,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1337,11 +1337,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B39,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B39,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B39,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B39,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1356,11 +1356,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B40,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B40,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B40,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B40,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1375,11 +1375,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B41,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B41,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B41,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B41,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1394,11 +1394,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B42,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B42,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B42,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B42,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1413,11 +1413,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B43,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B43,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B43,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B43,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1432,11 +1432,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B44,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B44,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B44,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B44,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1451,11 +1451,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B45,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B45,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B45,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B45,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1470,11 +1470,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B46,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B46,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B46,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B46,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1489,11 +1489,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B47,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B47,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B47,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B47,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1508,11 +1508,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B48,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B48,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B48,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B48,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1527,11 +1527,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B49,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B49,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B49,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B49,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1546,11 +1546,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B50,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B50,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B50,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B50,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1565,11 +1565,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B51,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B51,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B51,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B51,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1584,11 +1584,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B52,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B52,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B52,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B52,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1603,11 +1603,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B53,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B53,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B53,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B53,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1622,11 +1622,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B54,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B54,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B54,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B54,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1641,11 +1641,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B55,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B55,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B55,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B55,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1660,11 +1660,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B56,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B56,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B56,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B56,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1679,11 +1679,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B57,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B57,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B57,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B57,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1698,11 +1698,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B58,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B58,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B58,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B58,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1717,11 +1717,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B59,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B59,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B59,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B59,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1736,11 +1736,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B60,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B60,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B60,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B60,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1755,11 +1755,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B61,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B61,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B61,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B61,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1774,11 +1774,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B62,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B62,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B62,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B62,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1793,11 +1793,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B63,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B63,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B63,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B63,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1812,11 +1812,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B64,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B64,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B64,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B64,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1831,11 +1831,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B65,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B65,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B65,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B65,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1850,11 +1850,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B66,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B66,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B66,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B66,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1869,11 +1869,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B67,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B67,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B67,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B67,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1888,11 +1888,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B68,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B68,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B68,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B68,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1907,11 +1907,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B69,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B69,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B69,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B69,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1926,11 +1926,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B70,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B70,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B70,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B70,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1945,11 +1945,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B71,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B71,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B71,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B71,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1964,11 +1964,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B72,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B72,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B72,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B72,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1983,11 +1983,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B73,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B73,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B73,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B73,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2002,11 +2002,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B74,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B74,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B74,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B74,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2021,11 +2021,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B75,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B75,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B75,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B75,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2040,11 +2040,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B76,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B76,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B76,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B76,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2059,11 +2059,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B77,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B77,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B77,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B77,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2078,11 +2078,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B78,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B78,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B78,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B78,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2097,11 +2097,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B79,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B79,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B79,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B79,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2116,11 +2116,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B80,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B80,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B80,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B80,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2135,11 +2135,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B81,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B81,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B81,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B81,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2154,11 +2154,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B82,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B82,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B82,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B82,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2173,11 +2173,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B83,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B83,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B83,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B83,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2192,11 +2192,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B84,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B84,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B84,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B84,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2211,11 +2211,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B85,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B85,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B85,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B85,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2230,11 +2230,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B86,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B86,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B86,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B86,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2249,11 +2249,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B87,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B87,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B87,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B87,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2268,11 +2268,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B88,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B88,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B88,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B88,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2287,11 +2287,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B89,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B89,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B89,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B89,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2306,11 +2306,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B90,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B90,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B90,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B90,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2325,11 +2325,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B91,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B91,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B91,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B91,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2344,11 +2344,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B92,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B92,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B92,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B92,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2363,11 +2363,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B93,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B93,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B93,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B93,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2382,11 +2382,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B94,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B94,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B94,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B94,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2401,11 +2401,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B95,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B95,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B95,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B95,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2420,11 +2420,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B96,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B96,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B96,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B96,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2439,11 +2439,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B97,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B97,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B97,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B97,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2458,11 +2458,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B98,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B98,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B98,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B98,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2477,11 +2477,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B99,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B99,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B99,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B99,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2496,11 +2496,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B100,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B100,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B100,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B100,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2515,11 +2515,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B101,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B101,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B101,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B101,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2534,11 +2534,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B102,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B102,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B102,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B102,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2553,11 +2553,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B103,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B103,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B103,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B103,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2572,11 +2572,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B104,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B104,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B104,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B104,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2591,11 +2591,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B105,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B105,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B105,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B105,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2610,11 +2610,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B106,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B106,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B106,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B106,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2629,11 +2629,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B107,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B107,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B107,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B107,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2648,11 +2648,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B108,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B108,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B108,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B108,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2667,11 +2667,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B109,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B109,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B109,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B109,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2686,11 +2686,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B110,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B110,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B110,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B110,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2705,11 +2705,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B111,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B111,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B111,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B111,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2724,11 +2724,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B112,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B112,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B112,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B112,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2743,11 +2743,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B113,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B113,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B113,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B113,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2762,11 +2762,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B114,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B114,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B114,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B114,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2781,11 +2781,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B115,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B115,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B115,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B115,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2800,11 +2800,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B116,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B116,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B116,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B116,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2819,11 +2819,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B117,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B117,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B117,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B117,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2838,11 +2838,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B118,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B118,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B118,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B118,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2857,11 +2857,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B119,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B119,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B119,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B119,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2876,11 +2876,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B120,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B120,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B120,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B120,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2895,11 +2895,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B121,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B121,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B121,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B121,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2914,11 +2914,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B122,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B122,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B122,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B122,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2933,11 +2933,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B123,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B123,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B123,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B123,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2952,11 +2952,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B124,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B124,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B124,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B124,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2971,11 +2971,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B125,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B125,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B125,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B125,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -2990,11 +2990,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B126,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B126,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B126,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B126,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3009,11 +3009,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B127,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B127,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B127,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B127,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3028,11 +3028,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B128,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B128,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B128,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B128,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3047,11 +3047,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B129,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B129,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B129,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B129,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3066,11 +3066,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B130,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B130,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B130,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B130,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3085,11 +3085,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B131,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B131,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B131,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B131,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3104,11 +3104,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B132,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B132,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B132,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B132,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3123,11 +3123,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B133,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B133,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B133,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B133,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3142,11 +3142,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B134,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B134,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B134,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B134,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3161,11 +3161,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B135,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B135,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B135,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B135,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3180,11 +3180,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B136,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B136,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B136,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B136,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3199,11 +3199,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B137,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B137,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B137,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B137,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3218,11 +3218,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B138,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B138,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B138,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B138,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3237,11 +3237,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B139,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B139,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B139,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B139,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3256,11 +3256,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B140,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B140,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B140,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B140,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3275,11 +3275,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B141,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B141,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B141,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B141,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3294,11 +3294,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B142,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B142,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B142,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B142,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3313,11 +3313,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B143,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B143,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B143,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B143,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3332,11 +3332,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B144,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B144,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B144,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B144,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3351,11 +3351,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B145,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B145,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B145,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B145,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3370,11 +3370,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B146,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B146,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B146,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B146,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3389,11 +3389,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B147,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B147,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B147,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B147,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3408,11 +3408,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B148,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B148,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B148,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B148,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3427,11 +3427,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B149,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B149,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B149,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B149,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3446,11 +3446,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B150,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B150,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B150,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B150,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3465,11 +3465,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B151,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B151,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B151,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B151,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3484,11 +3484,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B152,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B152,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B152,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B152,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3503,11 +3503,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B153,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B153,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B153,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B153,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3522,11 +3522,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B154,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B154,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B154,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B154,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3541,11 +3541,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B155,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B155,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B155,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B155,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3560,11 +3560,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B156,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B156,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B156,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B156,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3579,11 +3579,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B157,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B157,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B157,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B157,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3598,11 +3598,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B158,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B158,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B158,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B158,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3617,11 +3617,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B159,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B159,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B159,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B159,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3636,11 +3636,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B160,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B160,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B160,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B160,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3655,11 +3655,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B161,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B161,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B161,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B161,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3674,11 +3674,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B162,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B162,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B162,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B162,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3693,11 +3693,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B163,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B163,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B163,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B163,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3712,11 +3712,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B164,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B164,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B164,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B164,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3731,11 +3731,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B165,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B165,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B165,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B165,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3750,11 +3750,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B166,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B166,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B166,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B166,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3769,11 +3769,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B167,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B167,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B167,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B167,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3788,11 +3788,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B168,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B168,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B168,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B168,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3807,11 +3807,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B169,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B169,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B169,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B169,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3826,11 +3826,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B170,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B170,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B170,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B170,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3845,11 +3845,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B171,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B171,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B171,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B171,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3864,11 +3864,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B172,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B172,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B172,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B172,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3883,11 +3883,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B173,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B173,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B173,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B173,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3902,11 +3902,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B174,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B174,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B174,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B174,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3921,11 +3921,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B175,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B175,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B175,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B175,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3940,11 +3940,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B176,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B176,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B176,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B176,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3959,11 +3959,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B177,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B177,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B177,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B177,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3978,11 +3978,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B178,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B178,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B178,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B178,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -3997,11 +3997,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B179,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B179,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B179,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B179,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4016,11 +4016,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B180,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B180,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B180,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B180,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4035,11 +4035,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B181,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B181,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B181,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B181,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4054,11 +4054,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B182,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B182,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B182,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B182,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4073,11 +4073,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B183,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B183,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B183,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B183,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4092,11 +4092,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B184,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B184,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B184,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B184,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4111,11 +4111,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B185,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B185,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B185,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B185,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4130,11 +4130,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B186,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B186,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B186,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B186,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4149,11 +4149,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B187,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B187,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B187,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B187,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4168,11 +4168,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B188,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B188,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B188,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B188,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4187,11 +4187,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B189,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B189,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B189,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B189,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4206,11 +4206,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B190,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B190,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B190,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B190,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4225,11 +4225,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B191,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B191,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B191,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B191,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4244,11 +4244,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B192,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B192,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B192,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B192,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4263,11 +4263,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B193,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B193,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B193,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B193,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4282,11 +4282,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B194,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B194,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B194,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B194,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4301,11 +4301,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B195,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B195,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B195,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B195,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4320,11 +4320,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B196,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B196,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B196,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B196,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4339,11 +4339,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B197,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B197,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B197,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B197,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4358,11 +4358,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B198,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B198,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B198,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B198,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4377,11 +4377,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B199,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B199,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B199,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B199,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4396,11 +4396,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B200,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B200,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B200,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B200,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4415,11 +4415,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B201,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B201,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B201,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B201,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4434,11 +4434,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B202,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B202,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B202,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B202,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4453,11 +4453,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B203,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B203,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B203,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B203,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4472,11 +4472,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B204,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B204,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B204,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B204,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4491,11 +4491,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B205,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B205,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B205,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B205,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4510,11 +4510,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B206,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B206,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B206,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B206,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4529,11 +4529,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B207,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B207,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B207,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B207,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4548,11 +4548,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B208,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B208,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B208,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B208,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4567,11 +4567,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B209,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B209,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B209,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B209,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4586,11 +4586,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B210,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B210,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B210,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B210,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4605,11 +4605,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B211,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B211,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B211,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B211,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4624,11 +4624,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B212,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B212,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B212,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B212,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4643,11 +4643,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B213,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B213,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B213,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B213,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4662,11 +4662,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B214,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B214,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B214,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B214,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4681,11 +4681,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B215,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B215,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B215,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B215,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4700,11 +4700,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B216,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B216,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B216,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B216,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4719,11 +4719,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B217,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B217,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B217,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B217,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4738,11 +4738,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B218,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B218,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B218,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B218,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4757,11 +4757,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B219,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B219,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B219,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B219,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4776,11 +4776,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B220,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B220,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B220,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B220,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4795,11 +4795,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B221,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B221,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B221,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B221,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4814,11 +4814,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B222,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B222,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B222,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B222,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4833,11 +4833,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B223,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B223,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B223,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B223,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4852,11 +4852,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B224,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B224,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B224,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B224,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4871,11 +4871,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B225,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B225,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B225,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B225,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4890,11 +4890,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B226,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B226,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B226,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B226,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4909,11 +4909,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B227,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B227,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B227,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B227,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4928,11 +4928,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B228,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B228,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B228,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B228,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4947,11 +4947,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B229,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B229,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B229,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B229,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4966,11 +4966,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B230,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B230,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B230,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B230,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4985,11 +4985,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B231,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B231,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B231,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B231,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5004,11 +5004,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B232,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B232,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B232,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B232,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5023,11 +5023,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B233,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B233,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B233,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B233,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5042,11 +5042,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B234,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B234,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B234,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B234,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5061,11 +5061,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B235,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B235,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B235,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B235,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5080,11 +5080,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B236,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B236,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B236,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B236,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5099,11 +5099,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B237,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B237,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B237,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B237,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5118,11 +5118,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B238,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B238,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B238,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B238,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5137,11 +5137,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B239,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B239,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B239,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B239,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5156,11 +5156,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B240,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B240,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B240,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B240,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5175,11 +5175,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B241,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B241,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B241,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B241,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5194,11 +5194,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B242,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B242,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B242,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B242,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5213,11 +5213,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B243,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B243,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B243,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B243,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5232,11 +5232,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B244,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B244,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B244,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B244,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5251,11 +5251,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B245,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B245,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B245,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B245,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5270,11 +5270,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B246,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B246,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B246,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B246,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5289,11 +5289,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B247,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B247,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B247,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B247,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5308,11 +5308,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B248,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B248,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B248,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B248,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5327,11 +5327,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B249,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B249,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B249,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B249,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5346,11 +5346,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B250,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B250,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B250,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B250,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5365,11 +5365,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B251,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B251,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B251,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B251,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5384,11 +5384,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B252,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B252,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B252,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B252,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5403,11 +5403,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B253,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B253,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B253,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B253,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5422,11 +5422,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B254,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B254,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B254,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B254,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5441,11 +5441,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B255,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B255,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B255,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B255,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5460,11 +5460,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B256,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B256,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B256,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B256,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5479,11 +5479,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B257,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B257,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B257,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B257,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5498,11 +5498,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B258,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B258,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B258,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B258,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5517,11 +5517,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B259,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B259,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B259,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B259,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5536,11 +5536,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B260,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B260,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B260,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B260,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5555,11 +5555,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B261,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B261,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B261,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B261,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5574,11 +5574,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B262,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B262,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B262,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B262,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5593,11 +5593,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B263,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B263,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B263,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B263,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5612,11 +5612,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B264,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B264,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B264,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B264,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5631,11 +5631,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B265,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B265,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B265,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B265,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5650,11 +5650,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B266,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B266,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B266,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B266,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5669,11 +5669,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B267,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B267,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B267,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B267,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5688,11 +5688,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B268,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B268,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B268,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B268,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5707,11 +5707,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B269,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B269,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B269,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B269,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5726,11 +5726,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B270,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B270,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B270,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B270,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5745,11 +5745,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B271,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B271,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B271,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B271,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5764,11 +5764,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B272,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B272,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B272,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B272,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5783,11 +5783,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B273,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B273,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B273,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B273,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5802,11 +5802,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B274,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B274,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B274,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B274,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5821,11 +5821,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B275,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B275,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B275,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B275,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5840,11 +5840,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B276,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B276,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B276,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B276,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5859,11 +5859,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B277,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B277,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B277,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B277,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5878,11 +5878,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B278,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B278,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B278,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B278,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5897,11 +5897,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B279,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B279,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B279,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B279,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5916,11 +5916,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B280,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B280,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B280,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B280,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5935,11 +5935,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B281,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B281,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B281,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B281,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5954,11 +5954,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B282,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B282,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B282,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B282,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5973,11 +5973,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B283,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B283,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B283,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B283,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -5992,11 +5992,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B284,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B284,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B284,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B284,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6011,11 +6011,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B285,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B285,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B285,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B285,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6030,11 +6030,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B286,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B286,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B286,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B286,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6049,11 +6049,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B287,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B287,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B287,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B287,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6068,11 +6068,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B288,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B288,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B288,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B288,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6087,11 +6087,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B289,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B289,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B289,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B289,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6106,11 +6106,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B290,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B290,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B290,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B290,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6125,11 +6125,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B291,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B291,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B291,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B291,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6144,11 +6144,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B292,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B292,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B292,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B292,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6163,11 +6163,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B293,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B293,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B293,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B293,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6182,11 +6182,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B294,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B294,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B294,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B294,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6201,11 +6201,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B295,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B295,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B295,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B295,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6220,11 +6220,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B296,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B296,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B296,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B296,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6239,11 +6239,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B297,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B297,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B297,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B297,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6258,11 +6258,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B298,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B298,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B298,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B298,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6277,11 +6277,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B299,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B299,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B299,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B299,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6296,11 +6296,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B300,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B300,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B300,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B300,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6315,11 +6315,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B301,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B301,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B301,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B301,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6334,11 +6334,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B302,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B302,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B302,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B302,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6353,11 +6353,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B303,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B303,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B303,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B303,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6372,11 +6372,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B304,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B304,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B304,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B304,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6391,11 +6391,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B305,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B305,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B305,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B305,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6410,11 +6410,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B306,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B306,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B306,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B306,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6429,11 +6429,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B307,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B307,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B307,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B307,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6448,11 +6448,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B308,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B308,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B308,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B308,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6467,11 +6467,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B309,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B309,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B309,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B309,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6486,11 +6486,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B310,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B310,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B310,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B310,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6505,11 +6505,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B311,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B311,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B311,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B311,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6524,11 +6524,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B312,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B312,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B312,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B312,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6543,11 +6543,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B313,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B313,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B313,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B313,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6562,11 +6562,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B314,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B314,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B314,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B314,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6581,11 +6581,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B315,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B315,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B315,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B315,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6600,11 +6600,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B316,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B316,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B316,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B316,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6619,11 +6619,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B317,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B317,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B317,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B317,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6638,11 +6638,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B318,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B318,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B318,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B318,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6657,11 +6657,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B319,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B319,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B319,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B319,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6676,11 +6676,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B320,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B320,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B320,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B320,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6695,11 +6695,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B321,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B321,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B321,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B321,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6714,11 +6714,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B322,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B322,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B322,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B322,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6733,11 +6733,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B323,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B323,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B323,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B323,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6752,11 +6752,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B324,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B324,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B324,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B324,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6771,11 +6771,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B325,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B325,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B325,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B325,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6790,11 +6790,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B326,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B326,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B326,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B326,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6809,11 +6809,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B327,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B327,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B327,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B327,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6828,11 +6828,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B328,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B328,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B328,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B328,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6847,11 +6847,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B329,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B329,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B329,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B329,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6866,11 +6866,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B330,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B330,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B330,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B330,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6885,11 +6885,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B331,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B331,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B331,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B331,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6904,11 +6904,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B332,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B332,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B332,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B332,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6923,11 +6923,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B333,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B333,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B333,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B333,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6942,11 +6942,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B334,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B334,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B334,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B334,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6961,11 +6961,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B335,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B335,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B335,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B335,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6980,11 +6980,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B336,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B336,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B336,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B336,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -6999,11 +6999,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B337,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B337,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B337,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B337,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7018,11 +7018,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B338,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B338,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B338,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B338,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7037,11 +7037,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B339,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B339,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B339,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B339,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7056,11 +7056,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B340,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B340,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B340,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B340,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7075,11 +7075,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B341,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B341,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B341,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B341,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7094,11 +7094,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B342,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B342,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B342,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B342,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7113,11 +7113,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B343,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B343,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B343,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B343,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7132,11 +7132,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B344,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B344,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B344,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B344,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7151,11 +7151,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B345,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B345,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B345,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B345,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7170,11 +7170,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B346,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B346,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B346,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B346,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7189,11 +7189,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B347,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B347,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B347,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B347,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7208,11 +7208,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B348,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B348,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B348,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B348,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7227,11 +7227,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B349,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B349,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B349,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B349,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7246,11 +7246,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B350,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B350,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B350,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B350,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7265,11 +7265,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B351,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B351,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B351,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B351,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7284,11 +7284,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B352,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B352,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B352,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B352,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7303,11 +7303,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B353,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B353,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B353,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B353,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7322,11 +7322,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B354,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B354,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B354,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B354,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7341,11 +7341,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B355,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B355,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B355,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B355,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7360,11 +7360,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B356,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B356,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B356,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B356,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7379,11 +7379,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B357,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B357,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B357,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B357,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7398,11 +7398,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B358,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B358,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B358,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B358,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7417,11 +7417,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B359,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B359,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B359,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B359,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7436,11 +7436,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B360,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B360,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B360,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B360,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7455,11 +7455,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B361,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B361,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B361,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B361,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7474,11 +7474,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B362,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B362,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B362,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B362,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7493,11 +7493,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B363,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B363,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B363,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B363,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7512,11 +7512,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B364,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B364,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B364,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B364,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7531,11 +7531,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B365,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B365,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B365,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B365,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7550,11 +7550,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B366,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B366,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B366,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B366,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7569,11 +7569,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B367,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B367,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B367,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B367,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7588,11 +7588,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B368,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B368,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B368,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B368,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7607,11 +7607,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B369,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B369,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B369,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B369,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7626,11 +7626,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B370,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B370,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B370,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B370,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7645,11 +7645,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B371,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B371,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B371,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B371,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7664,11 +7664,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B372,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B372,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B372,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B372,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7683,11 +7683,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B373,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B373,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B373,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B373,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7702,11 +7702,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B374,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B374,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B374,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B374,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7721,11 +7721,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B375,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B375,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B375,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B375,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7740,11 +7740,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B376,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B376,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B376,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B376,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7759,11 +7759,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B377,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B377,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B377,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B377,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7778,11 +7778,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B378,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B378,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B378,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B378,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7797,11 +7797,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B379,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B379,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B379,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B379,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7816,11 +7816,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B380,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B380,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B380,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B380,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7835,11 +7835,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B381,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B381,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B381,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B381,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7854,11 +7854,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B382,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B382,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B382,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B382,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7873,11 +7873,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B383,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B383,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B383,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B383,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7892,11 +7892,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B384,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B384,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B384,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B384,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7911,11 +7911,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B385,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B385,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B385,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B385,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7930,11 +7930,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B386,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B386,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B386,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B386,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7949,11 +7949,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B387,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B387,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B387,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B387,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7968,11 +7968,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B388,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B388,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B388,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B388,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -7987,11 +7987,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B389,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B389,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B389,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B389,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8006,11 +8006,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B390,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B390,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B390,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B390,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8025,11 +8025,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B391,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B391,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B391,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B391,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8044,11 +8044,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B392,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B392,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B392,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B392,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8063,11 +8063,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B393,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B393,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B393,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B393,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8082,11 +8082,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B394,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B394,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B394,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B394,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8101,11 +8101,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B395,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B395,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B395,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B395,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8120,11 +8120,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B396,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B396,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B396,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B396,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8139,11 +8139,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B397,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B397,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B397,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B397,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8158,11 +8158,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B398,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B398,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B398,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B398,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8177,11 +8177,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B399,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B399,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B399,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B399,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8196,11 +8196,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B400,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B400,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B400,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B400,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8215,11 +8215,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B401,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B401,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B401,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B401,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8234,11 +8234,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$152,MATCH(B402,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B402,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$152,MATCH(B402,Productos!$A$2:$A$152,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B402,Productos!$A$2:$A$155,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
+          <t>ROYAL CANIN CARDIAC 2KG · 93504700000</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
+          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
+          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
+          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
+          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
         </is>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MEDIUM PUPPY 1 KG · 90405320000</t>
+          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
+          <t>ROYAL CANIN MEDIUM PUPPY 1 KG · 90405320000</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+          <t>ROYAL CANIN RENAL 2KG · 93510310000</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
+          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
         </is>
       </c>
     </row>
@@ -9135,6 +9135,11 @@
           <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9172,6 +9177,11 @@
           <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9207,6 +9217,11 @@
       <c r="S16" t="inlineStr">
         <is>
           <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>ROYALCANIN SATIETY 1.5KG · 93516260000</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10990,7 +11005,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -11130,7 +11145,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11270,7 +11285,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11710,7 +11725,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11910,7 +11925,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12221,16 +12236,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
+          <t>ROYAL CANIN CARDIAC 2KG · 93504700000</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>93505490000</t>
+          <t>93504700000</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12241,16 +12256,16 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
+          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>90006770000</t>
+          <t>93505490000</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12261,16 +12276,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
+          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>93505710000</t>
+          <t>90006770000</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12281,16 +12296,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
+          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>93505700000</t>
+          <t>93505710000</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12301,16 +12316,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
+          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>93505510000</t>
+          <t>93505700000</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12321,16 +12336,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>90006780000</t>
+          <t>93505510000</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12341,16 +12356,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MEDIUM PUPPY 1 KG · 90405320000</t>
+          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>90405320000</t>
+          <t>90006780000</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12361,12 +12376,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
+          <t>ROYAL CANIN MEDIUM PUPPY 1 KG · 90405320000</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>90006790000</t>
+          <t>90405320000</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -12381,16 +12396,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+          <t>ROYAL CANIN RENAL 2KG · 93510310000</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>93505570000</t>
+          <t>93510310000</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12401,16 +12416,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
+          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>90407030000</t>
+          <t>90006790000</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12421,12 +12436,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA M/MANI 1UD · 93513050000</t>
+          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>93513050000</t>
+          <t>93505570000</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -12434,19 +12449,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>ROYAL CANIN</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>D WS POLLO Y ARROZ INTEGRAL 16L · 93500000229</t>
+          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>93500000229</t>
+          <t>90407030000</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -12454,61 +12469,121 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SUNSHINE MILLS</t>
+          <t>ROYAL CANIN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>ROYALCANIN SATIETY 1.5KG · 93516260000</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93516260000</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>ROYAL CANIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>UC SNACK BARRA RELLENA M/MANI 1UD · 93513050000</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>93513050000</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sucursal</t>
+          <t>D WS POLLO Y ARROZ INTEGRAL 16L · 93500000229</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>P&amp;G | HOSPITAL COSTA VERDE</t>
+          <t>93500000229</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SUNSHINE MILLS</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>93500000342</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>6</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SUPERKAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>P&amp;G | HOSPITAL COSTA VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>Índice</t>
         </is>
       </c>
-      <c r="B155" t="n">
+      <c r="B158" t="n">
         <v>104</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>Inventario al</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>20.10.2026</t>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/104.xlsx
+++ b/plantillas/104.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="MARCA_1">Listas!$D$2:$D$5</definedName>
+    <definedName name="MARCA_1">Listas!$D$2:$D$4</definedName>
     <definedName name="MARCA_2">Listas!$E$2:$E$6</definedName>
     <definedName name="MARCA_3">Listas!$F$2:$F$26</definedName>
     <definedName name="MARCA_4">Listas!$G$2:$G$5</definedName>
@@ -638,11 +638,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B3,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B3,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B3,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B3,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -662,11 +662,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B4,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B4,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B4,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B4,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -686,11 +686,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B5,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B5,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B5,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B5,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -710,11 +710,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B6,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B6,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B6,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B6,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -729,11 +729,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B7,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B7,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B7,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B7,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -748,11 +748,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B8,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B8,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B8,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B8,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -767,11 +767,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B9,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B9,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B9,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B9,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -786,11 +786,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B10,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B10,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B10,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B10,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -805,11 +805,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B11,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B11,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B11,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B11,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -824,11 +824,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B12,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B12,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B12,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B12,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -843,11 +843,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B13,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B13,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B13,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B13,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -862,11 +862,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B14,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B14,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B14,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B14,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -881,11 +881,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B15,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B15,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B15,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B15,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -900,11 +900,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B16,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B16,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B16,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B16,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -919,11 +919,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B17,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B17,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B17,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B17,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -938,11 +938,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B18,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B18,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B18,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B18,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -957,11 +957,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B19,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B19,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B19,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B19,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -976,11 +976,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B20,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B20,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B20,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B20,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -995,11 +995,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B21,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B21,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B21,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B21,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1014,11 +1014,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B22,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B22,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B22,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B22,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1033,11 +1033,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B23,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B23,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B23,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B23,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1052,11 +1052,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B24,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B24,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B24,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B24,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1071,11 +1071,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B25,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B25,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B25,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B25,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1090,11 +1090,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B26,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B26,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B26,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B26,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1109,11 +1109,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B27,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B27,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B27,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B27,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1128,11 +1128,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B28,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B28,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B28,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B28,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1147,11 +1147,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B29,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B29,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B29,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B29,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1166,11 +1166,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B30,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B30,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B30,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B30,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1185,11 +1185,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B31,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B31,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B31,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B31,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1204,11 +1204,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B32,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B32,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B32,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B32,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1223,11 +1223,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B33,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B33,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B33,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B33,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1242,11 +1242,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B34,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B34,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B34,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B34,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1261,11 +1261,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B35,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B35,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B35,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B35,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1280,11 +1280,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B36,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B36,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B36,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B36,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1299,11 +1299,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B37,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B37,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B37,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B37,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1318,11 +1318,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B38,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B38,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B38,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B38,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1337,11 +1337,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B39,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B39,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B39,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B39,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1356,11 +1356,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B40,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B40,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B40,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B40,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1375,11 +1375,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B41,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B41,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B41,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B41,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1394,11 +1394,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B42,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B42,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B42,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B42,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1413,11 +1413,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B43,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B43,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B43,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B43,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1432,11 +1432,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B44,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B44,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B44,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B44,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1451,11 +1451,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B45,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B45,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B45,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B45,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1470,11 +1470,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B46,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B46,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B46,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B46,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1489,11 +1489,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B47,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B47,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B47,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B47,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1508,11 +1508,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B48,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B48,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B48,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B48,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1527,11 +1527,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B49,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B49,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B49,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B49,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1546,11 +1546,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B50,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B50,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B50,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B50,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1565,11 +1565,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B51,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B51,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B51,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B51,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1584,11 +1584,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B52,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B52,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B52,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B52,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1603,11 +1603,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B53,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B53,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B53,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B53,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1622,11 +1622,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B54,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B54,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B54,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B54,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1641,11 +1641,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B55,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B55,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B55,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B55,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1660,11 +1660,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B56,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B56,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B56,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B56,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1679,11 +1679,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B57,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B57,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B57,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B57,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1698,11 +1698,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B58,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B58,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B58,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B58,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1717,11 +1717,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B59,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B59,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B59,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B59,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1736,11 +1736,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B60,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B60,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B60,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B60,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1755,11 +1755,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B61,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B61,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B61,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B61,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1774,11 +1774,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B62,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B62,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B62,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B62,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1793,11 +1793,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B63,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B63,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B63,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B63,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1812,11 +1812,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B64,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B64,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B64,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B64,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1831,11 +1831,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B65,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B65,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B65,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B65,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1850,11 +1850,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B66,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B66,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B66,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B66,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1869,11 +1869,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B67,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B67,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B67,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B67,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1888,11 +1888,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B68,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B68,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B68,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B68,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1907,11 +1907,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B69,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B69,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B69,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B69,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1926,11 +1926,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B70,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B70,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B70,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B70,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1945,11 +1945,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B71,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B71,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B71,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B71,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1964,11 +1964,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B72,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B72,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B72,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B72,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1983,11 +1983,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B73,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B73,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B73,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B73,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2002,11 +2002,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B74,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B74,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B74,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B74,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2021,11 +2021,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B75,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B75,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B75,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B75,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2040,11 +2040,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B76,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B76,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B76,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B76,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2059,11 +2059,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B77,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B77,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B77,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B77,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2078,11 +2078,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B78,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B78,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B78,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B78,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2097,11 +2097,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B79,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B79,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B79,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B79,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2116,11 +2116,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B80,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B80,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B80,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B80,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2135,11 +2135,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B81,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B81,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B81,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B81,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2154,11 +2154,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B82,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B82,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B82,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B82,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2173,11 +2173,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B83,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B83,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B83,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B83,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2192,11 +2192,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B84,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B84,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B84,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B84,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2211,11 +2211,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B85,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B85,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B85,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B85,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2230,11 +2230,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B86,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B86,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B86,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B86,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2249,11 +2249,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B87,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B87,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B87,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B87,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2268,11 +2268,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B88,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B88,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B88,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B88,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2287,11 +2287,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B89,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B89,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B89,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B89,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2306,11 +2306,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B90,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B90,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B90,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B90,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2325,11 +2325,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B91,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B91,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B91,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B91,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2344,11 +2344,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B92,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B92,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B92,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B92,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2363,11 +2363,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B93,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B93,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B93,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B93,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2382,11 +2382,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B94,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B94,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B94,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B94,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2401,11 +2401,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B95,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B95,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B95,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B95,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2420,11 +2420,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B96,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B96,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B96,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B96,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2439,11 +2439,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B97,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B97,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B97,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B97,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2458,11 +2458,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B98,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B98,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B98,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B98,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2477,11 +2477,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B99,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B99,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B99,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B99,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2496,11 +2496,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B100,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B100,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B100,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B100,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2515,11 +2515,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B101,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B101,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B101,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B101,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2534,11 +2534,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B102,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B102,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B102,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B102,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2553,11 +2553,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B103,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B103,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B103,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B103,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2572,11 +2572,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B104,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B104,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B104,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B104,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2591,11 +2591,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B105,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B105,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B105,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B105,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2610,11 +2610,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B106,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B106,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B106,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B106,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2629,11 +2629,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B107,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B107,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B107,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B107,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2648,11 +2648,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B108,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B108,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B108,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B108,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2667,11 +2667,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B109,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B109,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B109,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B109,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2686,11 +2686,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B110,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B110,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B110,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B110,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2705,11 +2705,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B111,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B111,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B111,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B111,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2724,11 +2724,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B112,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B112,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B112,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B112,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2743,11 +2743,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B113,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B113,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B113,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B113,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2762,11 +2762,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B114,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B114,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B114,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B114,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2781,11 +2781,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B115,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B115,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B115,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B115,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2800,11 +2800,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B116,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B116,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B116,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B116,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2819,11 +2819,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B117,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B117,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B117,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B117,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2838,11 +2838,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B118,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B118,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B118,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B118,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2857,11 +2857,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B119,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B119,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B119,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B119,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2876,11 +2876,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B120,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B120,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B120,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B120,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2895,11 +2895,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B121,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B121,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B121,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B121,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2914,11 +2914,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B122,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B122,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B122,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B122,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2933,11 +2933,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B123,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B123,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B123,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B123,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2952,11 +2952,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B124,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B124,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B124,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B124,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2971,11 +2971,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B125,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B125,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B125,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B125,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -2990,11 +2990,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B126,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B126,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B126,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B126,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3009,11 +3009,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B127,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B127,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B127,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B127,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3028,11 +3028,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B128,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B128,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B128,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B128,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3047,11 +3047,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B129,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B129,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B129,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B129,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3066,11 +3066,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B130,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B130,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B130,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B130,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3085,11 +3085,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B131,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B131,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B131,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B131,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3104,11 +3104,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B132,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B132,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B132,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B132,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3123,11 +3123,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B133,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B133,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B133,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B133,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3142,11 +3142,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B134,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B134,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B134,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B134,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3161,11 +3161,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B135,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B135,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B135,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B135,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3180,11 +3180,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B136,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B136,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B136,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B136,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3199,11 +3199,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B137,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B137,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B137,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B137,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3218,11 +3218,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B138,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B138,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B138,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B138,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3237,11 +3237,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B139,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B139,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B139,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B139,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3256,11 +3256,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B140,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B140,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B140,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B140,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3275,11 +3275,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B141,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B141,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B141,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B141,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3294,11 +3294,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B142,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B142,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B142,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B142,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3313,11 +3313,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B143,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B143,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B143,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B143,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3332,11 +3332,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B144,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B144,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B144,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B144,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3351,11 +3351,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B145,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B145,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B145,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B145,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3370,11 +3370,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B146,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B146,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B146,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B146,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3389,11 +3389,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B147,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B147,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B147,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B147,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3408,11 +3408,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B148,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B148,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B148,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B148,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3427,11 +3427,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B149,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B149,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B149,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B149,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3446,11 +3446,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B150,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B150,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B150,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B150,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3465,11 +3465,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B151,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B151,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B151,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B151,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3484,11 +3484,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B152,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B152,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B152,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B152,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3503,11 +3503,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B153,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B153,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B153,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B153,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3522,11 +3522,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B154,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B154,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B154,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B154,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3541,11 +3541,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B155,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B155,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B155,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B155,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3560,11 +3560,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B156,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B156,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B156,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B156,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3579,11 +3579,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B157,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B157,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B157,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B157,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3598,11 +3598,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B158,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B158,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B158,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B158,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3617,11 +3617,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B159,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B159,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B159,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B159,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3636,11 +3636,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B160,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B160,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B160,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B160,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3655,11 +3655,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B161,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B161,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B161,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B161,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3674,11 +3674,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B162,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B162,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B162,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B162,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3693,11 +3693,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B163,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B163,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B163,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B163,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3712,11 +3712,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B164,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B164,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B164,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B164,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3731,11 +3731,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B165,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B165,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B165,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B165,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3750,11 +3750,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B166,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B166,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B166,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B166,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3769,11 +3769,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B167,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B167,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B167,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B167,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3788,11 +3788,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B168,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B168,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B168,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B168,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3807,11 +3807,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B169,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B169,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B169,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B169,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3826,11 +3826,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B170,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B170,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B170,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B170,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3845,11 +3845,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B171,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B171,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B171,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B171,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3864,11 +3864,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B172,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B172,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B172,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B172,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3883,11 +3883,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B173,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B173,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B173,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B173,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3902,11 +3902,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B174,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B174,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B174,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B174,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3921,11 +3921,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B175,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B175,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B175,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B175,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3940,11 +3940,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B176,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B176,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B176,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B176,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3959,11 +3959,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B177,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B177,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B177,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B177,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3978,11 +3978,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B178,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B178,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B178,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B178,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -3997,11 +3997,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B179,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B179,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B179,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B179,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4016,11 +4016,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B180,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B180,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B180,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B180,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4035,11 +4035,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B181,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B181,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B181,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B181,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4054,11 +4054,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B182,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B182,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B182,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B182,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4073,11 +4073,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B183,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B183,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B183,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B183,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4092,11 +4092,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B184,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B184,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B184,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B184,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4111,11 +4111,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B185,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B185,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B185,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B185,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4130,11 +4130,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B186,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B186,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B186,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B186,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4149,11 +4149,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B187,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B187,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B187,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B187,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4168,11 +4168,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B188,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B188,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B188,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B188,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4187,11 +4187,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B189,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B189,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B189,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B189,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4206,11 +4206,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B190,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B190,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B190,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B190,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4225,11 +4225,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B191,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B191,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B191,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B191,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4244,11 +4244,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B192,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B192,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B192,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B192,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4263,11 +4263,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B193,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B193,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B193,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B193,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4282,11 +4282,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B194,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B194,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B194,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B194,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4301,11 +4301,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B195,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B195,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B195,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B195,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4320,11 +4320,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B196,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B196,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B196,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B196,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4339,11 +4339,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B197,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B197,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B197,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B197,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4358,11 +4358,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B198,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B198,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B198,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B198,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4377,11 +4377,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B199,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B199,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B199,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B199,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4396,11 +4396,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B200,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B200,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B200,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B200,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4415,11 +4415,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B201,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B201,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B201,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B201,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4434,11 +4434,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B202,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B202,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B202,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B202,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4453,11 +4453,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B203,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B203,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B203,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B203,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4472,11 +4472,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B204,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B204,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B204,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B204,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4491,11 +4491,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B205,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B205,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B205,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B205,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4510,11 +4510,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B206,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B206,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B206,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B206,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4529,11 +4529,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B207,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B207,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B207,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B207,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4548,11 +4548,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B208,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B208,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B208,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B208,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4567,11 +4567,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B209,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B209,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B209,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B209,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4586,11 +4586,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B210,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B210,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B210,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B210,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4605,11 +4605,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B211,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B211,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B211,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B211,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4624,11 +4624,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B212,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B212,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B212,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B212,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4643,11 +4643,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B213,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B213,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B213,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B213,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4662,11 +4662,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B214,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B214,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B214,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B214,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4681,11 +4681,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B215,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B215,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B215,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B215,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4700,11 +4700,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B216,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B216,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B216,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B216,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4719,11 +4719,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B217,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B217,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B217,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B217,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4738,11 +4738,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B218,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B218,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B218,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B218,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4757,11 +4757,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B219,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B219,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B219,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B219,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4776,11 +4776,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B220,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B220,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B220,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B220,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4795,11 +4795,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B221,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B221,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B221,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B221,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4814,11 +4814,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B222,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B222,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B222,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B222,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4833,11 +4833,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B223,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B223,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B223,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B223,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4852,11 +4852,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B224,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B224,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B224,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B224,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4871,11 +4871,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B225,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B225,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B225,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B225,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4890,11 +4890,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B226,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B226,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B226,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B226,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4909,11 +4909,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B227,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B227,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B227,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B227,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4928,11 +4928,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B228,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B228,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B228,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B228,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4947,11 +4947,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B229,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B229,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B229,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B229,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4966,11 +4966,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B230,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B230,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B230,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B230,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4985,11 +4985,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B231,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B231,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B231,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B231,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5004,11 +5004,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B232,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B232,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B232,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B232,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5023,11 +5023,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B233,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B233,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B233,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B233,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5042,11 +5042,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B234,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B234,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B234,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B234,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5061,11 +5061,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B235,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B235,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B235,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B235,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5080,11 +5080,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B236,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B236,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B236,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B236,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5099,11 +5099,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B237,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B237,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B237,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B237,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5118,11 +5118,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B238,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B238,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B238,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B238,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5137,11 +5137,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B239,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B239,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B239,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B239,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5156,11 +5156,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B240,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B240,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B240,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B240,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5175,11 +5175,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B241,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B241,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B241,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B241,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5194,11 +5194,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B242,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B242,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B242,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B242,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5213,11 +5213,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B243,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B243,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B243,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B243,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5232,11 +5232,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B244,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B244,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B244,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B244,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5251,11 +5251,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B245,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B245,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B245,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B245,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5270,11 +5270,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B246,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B246,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B246,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B246,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5289,11 +5289,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B247,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B247,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B247,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B247,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5308,11 +5308,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B248,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B248,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B248,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B248,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5327,11 +5327,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B249,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B249,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B249,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B249,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5346,11 +5346,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B250,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B250,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B250,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B250,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5365,11 +5365,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B251,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B251,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B251,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B251,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5384,11 +5384,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B252,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B252,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B252,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B252,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5403,11 +5403,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B253,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B253,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B253,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B253,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5422,11 +5422,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B254,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B254,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B254,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B254,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5441,11 +5441,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B255,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B255,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B255,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B255,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5460,11 +5460,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B256,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B256,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B256,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B256,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5479,11 +5479,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B257,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B257,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B257,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B257,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5498,11 +5498,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B258,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B258,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B258,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B258,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5517,11 +5517,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B259,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B259,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B259,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B259,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5536,11 +5536,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B260,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B260,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B260,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B260,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5555,11 +5555,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B261,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B261,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B261,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B261,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5574,11 +5574,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B262,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B262,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B262,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B262,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5593,11 +5593,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B263,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B263,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B263,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B263,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5612,11 +5612,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B264,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B264,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B264,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B264,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5631,11 +5631,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B265,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B265,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B265,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B265,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5650,11 +5650,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B266,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B266,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B266,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B266,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5669,11 +5669,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B267,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B267,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B267,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B267,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5688,11 +5688,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B268,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B268,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B268,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B268,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5707,11 +5707,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B269,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B269,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B269,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B269,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5726,11 +5726,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B270,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B270,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B270,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B270,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5745,11 +5745,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B271,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B271,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B271,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B271,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5764,11 +5764,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B272,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B272,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B272,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B272,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5783,11 +5783,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B273,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B273,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B273,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B273,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5802,11 +5802,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B274,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B274,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B274,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B274,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5821,11 +5821,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B275,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B275,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B275,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B275,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5840,11 +5840,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B276,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B276,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B276,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B276,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5859,11 +5859,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B277,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B277,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B277,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B277,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5878,11 +5878,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B278,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B278,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B278,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B278,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5897,11 +5897,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B279,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B279,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B279,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B279,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5916,11 +5916,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B280,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B280,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B280,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B280,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5935,11 +5935,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B281,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B281,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B281,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B281,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5954,11 +5954,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B282,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B282,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B282,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B282,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5973,11 +5973,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B283,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B283,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B283,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B283,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -5992,11 +5992,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B284,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B284,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B284,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B284,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6011,11 +6011,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B285,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B285,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B285,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B285,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6030,11 +6030,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B286,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B286,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B286,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B286,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6049,11 +6049,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B287,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B287,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B287,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B287,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6068,11 +6068,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B288,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B288,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B288,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B288,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6087,11 +6087,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B289,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B289,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B289,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B289,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6106,11 +6106,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B290,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B290,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B290,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B290,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6125,11 +6125,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B291,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B291,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B291,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B291,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6144,11 +6144,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B292,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B292,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B292,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B292,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6163,11 +6163,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B293,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B293,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B293,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B293,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6182,11 +6182,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B294,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B294,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B294,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B294,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6201,11 +6201,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B295,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B295,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B295,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B295,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6220,11 +6220,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B296,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B296,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B296,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B296,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6239,11 +6239,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B297,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B297,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B297,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B297,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6258,11 +6258,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B298,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B298,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B298,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B298,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6277,11 +6277,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B299,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B299,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B299,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B299,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6296,11 +6296,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B300,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B300,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B300,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B300,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6315,11 +6315,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B301,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B301,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B301,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B301,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6334,11 +6334,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B302,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B302,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B302,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B302,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6353,11 +6353,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B303,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B303,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B303,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B303,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6372,11 +6372,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B304,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B304,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B304,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B304,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6391,11 +6391,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B305,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B305,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B305,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B305,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6410,11 +6410,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B306,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B306,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B306,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B306,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6429,11 +6429,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B307,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B307,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B307,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B307,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6448,11 +6448,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B308,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B308,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B308,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B308,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6467,11 +6467,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B309,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B309,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B309,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B309,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6486,11 +6486,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B310,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B310,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B310,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B310,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6505,11 +6505,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B311,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B311,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B311,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B311,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6524,11 +6524,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B312,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B312,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B312,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B312,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6543,11 +6543,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B313,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B313,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B313,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B313,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6562,11 +6562,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B314,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B314,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B314,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B314,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6581,11 +6581,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B315,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B315,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B315,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B315,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6600,11 +6600,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B316,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B316,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B316,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B316,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6619,11 +6619,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B317,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B317,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B317,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B317,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6638,11 +6638,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B318,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B318,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B318,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B318,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6657,11 +6657,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B319,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B319,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B319,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B319,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6676,11 +6676,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B320,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B320,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B320,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B320,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6695,11 +6695,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B321,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B321,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B321,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B321,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6714,11 +6714,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B322,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B322,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B322,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B322,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6733,11 +6733,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B323,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B323,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B323,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B323,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6752,11 +6752,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B324,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B324,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B324,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B324,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6771,11 +6771,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B325,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B325,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B325,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B325,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6790,11 +6790,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B326,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B326,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B326,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B326,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6809,11 +6809,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B327,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B327,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B327,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B327,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6828,11 +6828,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B328,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B328,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B328,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B328,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6847,11 +6847,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B329,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B329,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B329,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B329,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6866,11 +6866,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B330,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B330,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B330,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B330,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6885,11 +6885,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B331,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B331,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B331,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B331,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6904,11 +6904,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B332,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B332,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B332,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B332,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6923,11 +6923,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B333,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B333,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B333,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B333,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6942,11 +6942,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B334,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B334,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B334,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B334,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6961,11 +6961,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B335,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B335,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B335,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B335,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6980,11 +6980,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B336,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B336,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B336,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B336,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -6999,11 +6999,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B337,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B337,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B337,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B337,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7018,11 +7018,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B338,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B338,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B338,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B338,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7037,11 +7037,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B339,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B339,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B339,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B339,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7056,11 +7056,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B340,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B340,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B340,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B340,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7075,11 +7075,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B341,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B341,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B341,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B341,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7094,11 +7094,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B342,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B342,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B342,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B342,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7113,11 +7113,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B343,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B343,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B343,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B343,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7132,11 +7132,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B344,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B344,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B344,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B344,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7151,11 +7151,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B345,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B345,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B345,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B345,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7170,11 +7170,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B346,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B346,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B346,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B346,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7189,11 +7189,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B347,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B347,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B347,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B347,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7208,11 +7208,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B348,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B348,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B348,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B348,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7227,11 +7227,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B349,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B349,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B349,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B349,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7246,11 +7246,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B350,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B350,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B350,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B350,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7265,11 +7265,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B351,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B351,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B351,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B351,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7284,11 +7284,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B352,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B352,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B352,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B352,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7303,11 +7303,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B353,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B353,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B353,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B353,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7322,11 +7322,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B354,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B354,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B354,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B354,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7341,11 +7341,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B355,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B355,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B355,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B355,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7360,11 +7360,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B356,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B356,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B356,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B356,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7379,11 +7379,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B357,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B357,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B357,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B357,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7398,11 +7398,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B358,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B358,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B358,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B358,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7417,11 +7417,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B359,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B359,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B359,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B359,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7436,11 +7436,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B360,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B360,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B360,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B360,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7455,11 +7455,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B361,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B361,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B361,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B361,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7474,11 +7474,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B362,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B362,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B362,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B362,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7493,11 +7493,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B363,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B363,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B363,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B363,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7512,11 +7512,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B364,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B364,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B364,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B364,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7531,11 +7531,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B365,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B365,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B365,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B365,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7550,11 +7550,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B366,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B366,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B366,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B366,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7569,11 +7569,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B367,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B367,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B367,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B367,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7588,11 +7588,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B368,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B368,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B368,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B368,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7607,11 +7607,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B369,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B369,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B369,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B369,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7626,11 +7626,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B370,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B370,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B370,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B370,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7645,11 +7645,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B371,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B371,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B371,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B371,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7664,11 +7664,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B372,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B372,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B372,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B372,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7683,11 +7683,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B373,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B373,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B373,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B373,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7702,11 +7702,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B374,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B374,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B374,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B374,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7721,11 +7721,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B375,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B375,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B375,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B375,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7740,11 +7740,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B376,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B376,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B376,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B376,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7759,11 +7759,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B377,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B377,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B377,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B377,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7778,11 +7778,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B378,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B378,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B378,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B378,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7797,11 +7797,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B379,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B379,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B379,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B379,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7816,11 +7816,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B380,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B380,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B380,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B380,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7835,11 +7835,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B381,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B381,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B381,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B381,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7854,11 +7854,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B382,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B382,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B382,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B382,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7873,11 +7873,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B383,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B383,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B383,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B383,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7892,11 +7892,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B384,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B384,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B384,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B384,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7911,11 +7911,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B385,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B385,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B385,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B385,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7930,11 +7930,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B386,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B386,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B386,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B386,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7949,11 +7949,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B387,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B387,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B387,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B387,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7968,11 +7968,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B388,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B388,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B388,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B388,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -7987,11 +7987,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B389,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B389,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B389,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B389,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8006,11 +8006,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B390,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B390,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B390,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B390,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8025,11 +8025,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B391,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B391,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B391,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B391,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8044,11 +8044,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B392,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B392,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B392,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B392,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8063,11 +8063,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B393,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B393,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B393,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B393,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8082,11 +8082,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B394,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B394,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B394,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B394,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8101,11 +8101,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B395,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B395,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B395,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B395,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8120,11 +8120,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B396,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B396,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B396,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B396,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8139,11 +8139,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B397,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B397,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B397,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B397,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8158,11 +8158,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B398,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B398,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B398,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B398,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8177,11 +8177,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B399,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B399,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B399,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B399,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8196,11 +8196,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B400,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B400,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B400,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B400,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8215,11 +8215,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B401,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B401,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B401,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B401,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8234,11 +8234,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$155,MATCH(B402,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$154,MATCH(B402,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$155,MATCH(B402,Productos!$A$2:$A$155,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$154,MATCH(B402,Productos!$A$2:$A$154,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ANNAMAET GF GATOS 4LB · 93500000201</t>
+          <t>ANNAMAET PIEL Y ESTOMAGO SENSIBLE 5LB · 93500000184</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ANNAMAET PIEL Y ESTOMAGO SENSIBLE 5LB · 93500000184</t>
+          <t>ANNAMAET RAZA PEQUENA 4 LB · 93500000183</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ANNAMAET RAZA PEQUENA 4 LB · 93500000183</t>
+          <t>D ANNAMAET EXTRA 26% 5LB · 93500000177</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8691,11 +8691,6 @@
       <c r="C5">
         <f>RIGHT("0"&amp;MONTH(EDATE(TODAY(),3)),2)&amp;"/"&amp;YEAR(EDATE(TODAY(),3))</f>
         <v/>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>D ANNAMAET EXTRA 26% 5LB · 93500000177</t>
-        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -9448,7 +9443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9476,16 +9471,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ANNAMAET GF GATOS 4LB · 93500000201</t>
+          <t>ANNAMAET PIEL Y ESTOMAGO SENSIBLE 5LB · 93500000184</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93500000201</t>
+          <t>93500000184</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -9496,16 +9491,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ANNAMAET PIEL Y ESTOMAGO SENSIBLE 5LB · 93500000184</t>
+          <t>ANNAMAET RAZA PEQUENA 4 LB · 93500000183</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93500000184</t>
+          <t>93500000183</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -9516,16 +9511,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANNAMAET RAZA PEQUENA 4 LB · 93500000183</t>
+          <t>D ANNAMAET EXTRA 26% 5LB · 93500000177</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>93500000183</t>
+          <t>93500000177</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -9536,36 +9531,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D ANNAMAET EXTRA 26% 5LB · 93500000177</t>
+          <t>BILJAC CACHORRO RAZA PEQUENA 6LB · 93503260000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>93500000177</t>
+          <t>93503260000</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ANNAMAET</t>
+          <t>BIL-JAC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BILJAC CACHORRO RAZA PEQUENA 6LB · 93503260000</t>
+          <t>BILJAC PICKY NO MORE RAZA PEQUENA 6 · 93516580000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>93503260000</t>
+          <t>93516580000</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9576,16 +9571,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BILJAC PICKY NO MORE RAZA PEQUENA 6 · 93516580000</t>
+          <t>BILJAC PIEL Y ESTOMAGO SENSIBLE 15LB · 93503280000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93516580000</t>
+          <t>93503280000</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -9596,16 +9591,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BILJAC PIEL Y ESTOMAGO SENSIBLE 15LB · 93503280000</t>
+          <t>BILJAC PIEL Y ESTÓMAGO SENSIBLE 6LB · 93503290000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>93503280000</t>
+          <t>93503290000</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9616,12 +9611,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BILJAC PIEL Y ESTÓMAGO SENSIBLE 6LB · 93503290000</t>
+          <t>BJ S SENSIBLE Y SIST INMUNE 6LB · 93518470000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>93503290000</t>
+          <t>93518470000</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -9636,36 +9631,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BJ S SENSIBLE Y SIST INMUNE 6LB · 93518470000</t>
+          <t>CS ALIM LATA  POLLOP/GATITO 5.5OZ · 93511230000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>93518470000</t>
+          <t>93511230000</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BIL-JAC</t>
+          <t>CHICKEN SOUP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CS ALIM LATA  POLLOP/GATITO 5.5OZ · 93511230000</t>
+          <t>CS ALIM LATA  POLLOP/GATO AD 5.5OZ · 93511240000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>93511230000</t>
+          <t>93511240000</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9676,16 +9671,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CS ALIM LATA  POLLOP/GATO AD 5.5OZ · 93511240000</t>
+          <t>CS ALIM LATA POLLO/GATO MATURE 5.5 · 93511250000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>93511240000</t>
+          <t>93511250000</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9696,16 +9691,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CS ALIM LATA POLLO/GATO MATURE 5.5 · 93511250000</t>
+          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>93511250000</t>
+          <t>93511170000</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9716,16 +9711,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
+          <t>CS ALIMENTO EN LATA P/CACHORRO 13OZ · 93511160000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>93511170000</t>
+          <t>93511160000</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9736,16 +9731,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/CACHORRO 13OZ · 93511160000</t>
+          <t>CS CLASSIC GATO PATE PAVO EN SALSA 5.5OZ · 93500000262</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>93511160000</t>
+          <t>93500000262</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9756,16 +9751,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE PAVO EN SALSA 5.5OZ · 93500000262</t>
+          <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>93500000262</t>
+          <t>93500000261</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9776,16 +9771,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
+          <t>CS CLASSIC GATO PATE POLLO Y PESCADO 5.5 · 93500000260</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>93500000261</t>
+          <t>93500000260</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9796,16 +9791,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE POLLO Y PESCADO 5.5 · 93500000260</t>
+          <t>CS CLASSIC GATO PATE SALMON EN SALSA 5.5 · 93500000263</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>93500000260</t>
+          <t>93500000263</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9816,16 +9811,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE SALMON EN SALSA 5.5 · 93500000263</t>
+          <t>CS CLASSIC MATURE POLLO RZ PQNA 4.5 · 93518630000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>93500000263</t>
+          <t>93518630000</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9836,16 +9831,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CS CLASSIC MATURE POLLO RZ PQNA 4.5 · 93518630000</t>
+          <t>CS CLASSIC POLLO P/ADULTO 4.5LB · 93511070000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>93518630000</t>
+          <t>93511070000</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9856,16 +9851,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/ADULTO 4.5LB · 93511070000</t>
+          <t>CS CLASSIC POLLO P/MATURE 4.5LB · 93511130000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>93511070000</t>
+          <t>93511130000</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9876,16 +9871,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/MATURE 4.5LB · 93511130000</t>
+          <t>CS CLASSIC POLLO/ GATITOS 4.5LB · 93511210000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>93511130000</t>
+          <t>93511210000</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9896,16 +9891,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO/ GATITOS 4.5LB · 93511210000</t>
+          <t>CS CLASSIC POLLO/ GATOS ADULT 4.5LB · 93511190000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>93511210000</t>
+          <t>93511190000</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9916,16 +9911,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO/ GATOS ADULT 4.5LB · 93511190000</t>
+          <t>CS GATO CTRL PESO Y SENIOR 4.5LB · 93500000252</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>93511190000</t>
+          <t>93500000252</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9936,12 +9931,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CS GATO CTRL PESO Y SENIOR 4.5LB · 93500000252</t>
+          <t>CS GF PERRO LATA PAVO, CAMOTE 13OZ · 93500000257</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>93500000252</t>
+          <t>93500000257</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -9956,16 +9951,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CS GF PERRO LATA PAVO, CAMOTE 13OZ · 93500000257</t>
+          <t>CS GF PERRO LATA POLLO, CARNE, VEGETALES · 93500000256</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>93500000257</t>
+          <t>93500000256</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9976,16 +9971,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CS GF PERRO LATA POLLO, CARNE, VEGETALES · 93500000256</t>
+          <t>CS GRAIN FREE CORDERO/PERRO 4 LB · 93514490000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>93500000256</t>
+          <t>93514490000</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9996,16 +9991,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE CORDERO/PERRO 4 LB · 93514490000</t>
+          <t>CS GRAIN FREE POLLO P/ GATOS 4LB · 93514590000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>93514490000</t>
+          <t>93514590000</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -10016,16 +10011,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE POLLO P/ GATOS 4LB · 93514590000</t>
+          <t>CS GRAIN FREE SALMON P/ GATOS 4LB · 93514610000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93514590000</t>
+          <t>93514610000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10036,16 +10031,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON P/ GATOS 4LB · 93514610000</t>
+          <t>CS GRAIN FREE SALMON P/PERRO 4 LB · 93514460000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93514610000</t>
+          <t>93514460000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -10056,16 +10051,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON P/PERRO 4 LB · 93514460000</t>
+          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93514460000</t>
+          <t>93514480000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10076,16 +10071,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
+          <t>CS PERR CTRL PESO ARROZ, POLLO, PAVO 4.5 · 93500000248</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93514480000</t>
+          <t>93500000248</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10096,16 +10091,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CS PERR CTRL PESO ARROZ, POLLO, PAVO 4.5 · 93500000248</t>
+          <t>CS SNACK CRUNCHY M MANI /PERRO 12OZ · 93514390000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93500000248</t>
+          <t>93514390000</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -10116,12 +10111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY M MANI /PERRO 12OZ · 93514390000</t>
+          <t>CS SNACK CRUNCHY TOCINO /PERRO 12OZ · 93514380000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93514390000</t>
+          <t>93514380000</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -10136,12 +10131,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY TOCINO /PERRO 12OZ · 93514380000</t>
+          <t>D ERA ADULTO RZ PQNA POLLO FAISN?N 2K · 93516670000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93514380000</t>
+          <t>93516670000</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -10149,23 +10144,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CHICKEN SOUP</t>
+          <t>ERA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>D ERA ADULTO RZ PQNA POLLO FAISN?N 2K · 93516670000</t>
+          <t>D ERA SYBARITE LATA ATUN/CERDO 400G · 93519110000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>93516670000</t>
+          <t>93519110000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -10176,16 +10171,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>D ERA SYBARITE LATA ATUN/CERDO 400G · 93519110000</t>
+          <t>ERA SYBARITE LATA CACHORROS 400G · 93519090000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93519110000</t>
+          <t>93519090000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -10196,16 +10191,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ERA SYBARITE LATA CACHORROS 400G · 93519090000</t>
+          <t>ERA SYBARITE LATAPOLLO/PESCADO 400G · 93519100000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93519090000</t>
+          <t>93519100000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -10216,36 +10211,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ERA SYBARITE LATAPOLLO/PESCADO 400G · 93519100000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93519100000</t>
+          <t>90311050000</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ERA</t>
+          <t>ESBILAC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>KMR PAPILLA P GATITOS 2STEP 14 OZ. · 90404010000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90311050000</t>
+          <t>90404010000</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10256,16 +10251,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KMR PAPILLA P GATITOS 2STEP 14 OZ. · 90404010000</t>
+          <t>PA VITAM/MINERALES GEL P/GATO · 90330330000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90404010000</t>
+          <t>90330330000</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -10276,16 +10271,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PA VITAM/MINERALES GEL P/GATO · 90330330000</t>
+          <t>PA VITAMINA EN GEL CALORIAS P/GATO · 90330310000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90330330000</t>
+          <t>90330310000</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10296,16 +10291,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PA VITAMINA EN GEL CALORIAS P/GATO · 90330310000</t>
+          <t>PA VITAMINA EN GEL CALORIAS P/PERRO · 90330290000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90330310000</t>
+          <t>90330290000</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10316,16 +10311,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PA VITAMINA EN GEL CALORIAS P/PERRO · 90330290000</t>
+          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>90330290000</t>
+          <t>90308700000</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10336,32 +10331,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
+          <t>D 3 BEARS ALIMENTO LIOFILIZA PESCADO 1LB · 93500000210</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>90308700000</t>
+          <t>93500000210</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>GRANDMA LUCY'S</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D 3 BEARS ALIMENTO LIOFILIZA PESCADO 1LB · 93500000210</t>
+          <t>D 3 BEARS ALIMENTO LIOFILIZADO CARNE 1LB · 93500000208</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>93500000210</t>
+          <t>93500000208</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -10376,76 +10371,76 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D 3 BEARS ALIMENTO LIOFILIZADO CARNE 1LB · 93500000208</t>
+          <t>GM COUNT NAT ESTOMAG SENSIBLE/ PERRO 4LB · 93500000142</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>93500000208</t>
+          <t>93500000142</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GRANDMA LUCY'S</t>
+          <t>GRANDMA MAE'S</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GM COUNT NAT ESTOMAG SENSIBLE/ PERRO 4LB · 93500000142</t>
+          <t>SD ADULTO INDOOR FELINO 3.5LB · 93506540000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>93500000142</t>
+          <t>93506540000</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GRANDMA MAE'S</t>
+          <t>HILL'S</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SD ADULTO INDOOR FELINO 3.5LB · 93506540000</t>
+          <t>KORDON VITAMINA C PARA COBAYOS 2OZ · 90310300000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>93506540000</t>
+          <t>90310300000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HILL'S</t>
+          <t>KORDON</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KORDON VITAMINA C PARA COBAYOS 2OZ · 90310300000</t>
+          <t>KORDON VITAMINAS AVES PEQUENAS 2 OZ · 90720870000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>90310300000</t>
+          <t>90720870000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -10456,16 +10451,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS AVES PEQUENAS 2 OZ · 90720870000</t>
+          <t>KORDON VITAMINAS P COBAYOS 2 OZ · 90720790000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90720870000</t>
+          <t>90720790000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10476,16 +10471,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS P COBAYOS 2 OZ · 90720790000</t>
+          <t>KORDON VITAMINAS P CONEJO 2 OZ · 90720780000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>90720790000</t>
+          <t>90720780000</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -10496,56 +10491,56 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS P CONEJO 2 OZ · 90720780000</t>
+          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90720780000</t>
+          <t>90322670000</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>90322670000</t>
+          <t>93505920000</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>93505920000</t>
+          <t>90410730000</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10556,36 +10551,36 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>D NV ELECTROLITOS P/ PERROS/GATOS 16 · 90328660000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>90410730000</t>
+          <t>90328660000</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRI-VET</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D NV ELECTROLITOS P/ PERROS/GATOS 16 · 90328660000</t>
+          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>90328660000</t>
+          <t>90328330000</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10596,16 +10591,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
+          <t>D NV PASTILLA MASTICABLE P/VEJIGA 60U · 93518700000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>90328330000</t>
+          <t>93518700000</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10616,12 +10611,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>D NV PASTILLA MASTICABLE P/VEJIGA 60U · 93518700000</t>
+          <t>D NV SUPLEMEN HONGOS P/SISTEMA INMUNE · 90332570000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>93518700000</t>
+          <t>90332570000</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -10636,16 +10631,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>D NV SUPLEMEN HONGOS P/SISTEMA INMUNE · 90332570000</t>
+          <t>D NV SUPLEMENTO ANTI COPROFAGIA 500 · 90328650000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90332570000</t>
+          <t>90328650000</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10656,16 +10651,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>D NV SUPLEMENTO ANTI COPROFAGIA 500 · 90328650000</t>
+          <t>D NV TABLET PERR SENIOR MALESTAR/DOL · 90328760000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90328650000</t>
+          <t>90328760000</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -10676,16 +10671,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>D NV TABLET PERR SENIOR MALESTAR/DOL · 90328760000</t>
+          <t>D NV VITAMINA P/ TRACTO DIGESTIVO 60U · 90328340000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>90328760000</t>
+          <t>90328340000</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -10696,16 +10691,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>D NV VITAMINA P/ TRACTO DIGESTIVO 60U · 90328340000</t>
+          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90328340000</t>
+          <t>90327410000</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10716,16 +10711,16 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
+          <t>NV ENZIMAS DIGESTIVAS P/PERROS 70UD · 90327670000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>90327410000</t>
+          <t>90327670000</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10736,16 +10731,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NV ENZIMAS DIGESTIVAS P/PERROS 70UD · 90327670000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>90327670000</t>
+          <t>90327780000</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10756,16 +10751,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>90327780000</t>
+          <t>90328050000</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10776,16 +10771,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
+          <t>NV HIP N JOINT CON OMEGA P/GATO 60U · 90328310000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>90328050000</t>
+          <t>90328310000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -10796,16 +10791,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NV HIP N JOINT CON OMEGA P/GATO 60U · 90328310000</t>
+          <t>NV HIP N JOINT MASTICABLE 120UD · 90328300000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>90328310000</t>
+          <t>90328300000</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -10816,16 +10811,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NV HIP N JOINT MASTICABLE 120UD · 90328300000</t>
+          <t>NV PAST MAST CON ARANDANO P/GATO 60 · 90327630000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>90328300000</t>
+          <t>90327630000</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10836,16 +10831,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NV PAST MAST CON ARANDANO P/GATO 60 · 90327630000</t>
+          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>90327630000</t>
+          <t>90327640000</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10856,16 +10851,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
+          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>90327640000</t>
+          <t>90328780000</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10876,16 +10871,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
+          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>90328780000</t>
+          <t>90328700000</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10896,16 +10891,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
+          <t>NV TRANQUILIZANTE MAST P/PERRO 70 · 90328740000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>90328700000</t>
+          <t>90328740000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10916,16 +10911,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST P/PERRO 70 · 90328740000</t>
+          <t>NV TRANQUILIZANTE MAST PERRO SENIOR · 90328770000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>90328740000</t>
+          <t>90328770000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10936,16 +10931,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST PERRO SENIOR · 90328770000</t>
+          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>90328770000</t>
+          <t>90328860000</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10956,16 +10951,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
+          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>90328860000</t>
+          <t>90328840000</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10976,16 +10971,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
+          <t>NV VITAMINAS MAST P/PERROS 60 · 90327290000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>90328840000</t>
+          <t>90327290000</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10996,36 +10991,36 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NV VITAMINAS MAST P/PERROS 60 · 90327290000</t>
+          <t>NS CACHORRO RZ GDE GF 12LB · 93500000457</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>90327290000</t>
+          <t>93500000457</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE GF 12LB · 93500000457</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 12LB · 93500000460</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>93500000457</t>
+          <t>93500000460</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11036,16 +11031,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 12LB · 93500000460</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>93500000460</t>
+          <t>93500000461</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11056,16 +11051,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
+          <t>NS CTRL PESO PERRO POLLO 12LB · 93500000416</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>93500000461</t>
+          <t>93500000416</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11076,12 +11071,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NS CTRL PESO PERRO POLLO 12LB · 93500000416</t>
+          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>93500000416</t>
+          <t>93500000469</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -11096,16 +11091,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>93500000469</t>
+          <t>93500000471</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11116,16 +11111,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
+          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>93500000471</t>
+          <t>93500000488</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11136,16 +11131,16 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
+          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>93500000488</t>
+          <t>93500000486</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11156,16 +11151,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
+          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>93500000486</t>
+          <t>93500000487</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11176,16 +11171,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
+          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>93500000487</t>
+          <t>93500000475</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11196,16 +11191,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
+          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>93500000475</t>
+          <t>93500000472</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11216,16 +11211,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
+          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>93500000472</t>
+          <t>93500000468</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11236,16 +11231,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
+          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>93500000468</t>
+          <t>93500000467</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11256,16 +11251,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
+          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>93500000467</t>
+          <t>93500000473</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11276,16 +11271,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
+          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>93500000473</t>
+          <t>93500000466</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11296,16 +11291,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
+          <t>NS PERRO CORDERO Y ARROZ 26LB · 93500000436</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>93500000466</t>
+          <t>93500000436</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11316,16 +11311,16 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 26LB · 93500000436</t>
+          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>93500000436</t>
+          <t>93500000451</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11336,16 +11331,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
+          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>93500000451</t>
+          <t>93500000463</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11356,16 +11351,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>93500000463</t>
+          <t>93500000464</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,16 +11371,16 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO GF POLLO GUISANTE 12LB · 93500000441</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>93500000464</t>
+          <t>93500000441</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11396,16 +11391,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO GUISANTE 12LB · 93500000441</t>
+          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>93500000441</t>
+          <t>93500000442</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11416,16 +11411,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>93500000442</t>
+          <t>93500000449</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11436,12 +11431,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
+          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>93500000449</t>
+          <t>93500000438</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -11456,12 +11451,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
+          <t>NS PERRO SENIOR GF 4LB · 93500000455</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>93500000438</t>
+          <t>93500000455</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -11476,16 +11471,16 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NS PERRO SENIOR GF 4LB · 93500000455</t>
+          <t>NS PRAIRIE SELECT GF P PERROS 12LB · 90035700000</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>93500000455</t>
+          <t>90035700000</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11496,16 +11491,16 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NS PRAIRIE SELECT GF P PERROS 12LB · 90035700000</t>
+          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>90035700000</t>
+          <t>93500000496</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11516,36 +11511,36 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
+          <t>M MENUD NY SNACK FILET MIG 9350459 · 93515560000</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>93500000496</t>
+          <t>93515560000</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>M MENUD NY SNACK FILET MIG 9350459 · 93515560000</t>
+          <t>NY SNACK DENTAL 1CT · 93500000332</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>93515560000</t>
+          <t>93500000332</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11556,16 +11551,16 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL 1CT · 93500000332</t>
+          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>93500000332</t>
+          <t>93504600000</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11576,36 +11571,36 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
+          <t>PD GATO PRESC MULTICARE 4LB · 90411220000</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>93504600000</t>
+          <t>90411220000</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>PRESCRIPTION DIET</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PD GATO PRESC MULTICARE 4LB · 90411220000</t>
+          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>90411220000</t>
+          <t>90304010000</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11616,16 +11611,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
+          <t>SD CANINE K/D 8.5LB · 90303990000</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>90304010000</t>
+          <t>90303990000</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11636,16 +11631,16 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SD CANINE K/D 8.5LB · 90303990000</t>
+          <t>SD CANINE/FELINE A/D 5.5 OZ. · 90304470000</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>90303990000</t>
+          <t>90304470000</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11656,16 +11651,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SD CANINE/FELINE A/D 5.5 OZ. · 90304470000</t>
+          <t>SD FELINE K/D 4 LB · 90402960000</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>90304470000</t>
+          <t>90402960000</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11676,16 +11671,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SD FELINE K/D 4 LB · 90402960000</t>
+          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>90402960000</t>
+          <t>90406520000</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11696,16 +11691,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
+          <t>SD LATA CANINE W/D12/13OZ · 90406510000</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>90406520000</t>
+          <t>90406510000</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11716,16 +11711,16 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SD LATA CANINE W/D12/13OZ · 90406510000</t>
+          <t>SD LATA FELINE K/D 5.5OZ · 90409360000</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>90406510000</t>
+          <t>90409360000</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11736,16 +11731,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SD LATA FELINE K/D 5.5OZ · 90409360000</t>
+          <t>SD PD CANINDE C/D LATA 12OZ · 93517020000</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>90409360000</t>
+          <t>93517020000</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11756,16 +11751,16 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SD PD CANINDE C/D LATA 12OZ · 93517020000</t>
+          <t>SD PD CANINE METABOLISMO 7LB · 93517000000</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>93517020000</t>
+          <t>93517000000</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11776,16 +11771,16 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SD PD CANINE METABOLISMO 7LB · 93517000000</t>
+          <t>SD PD CANINE R/D 3.3LB · 93516970000</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>93517000000</t>
+          <t>93516970000</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11796,16 +11791,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SD PD CANINE R/D 3.3LB · 93516970000</t>
+          <t>SD PD GATO GASTROINTESTINAL 5.5OZ · 93517080000</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>93516970000</t>
+          <t>93517080000</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11816,16 +11811,16 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SD PD GATO GASTROINTESTINAL 5.5OZ · 93517080000</t>
+          <t>SD PD GATO I/D 4LB · 93517090000</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>93517080000</t>
+          <t>93517090000</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11836,16 +11831,16 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SD PD GATO I/D 4LB · 93517090000</t>
+          <t>SD PD GATO I/D LATA 5.5OZ · 93517100000</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>93517090000</t>
+          <t>93517100000</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11856,16 +11851,16 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SD PD GATO I/D LATA 5.5OZ · 93517100000</t>
+          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>93517100000</t>
+          <t>93517060000</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11876,36 +11871,36 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
+          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>93517060000</t>
+          <t>90009660000</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PRESCRIPTION DIET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
+          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>90009660000</t>
+          <t>90009650000</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11916,16 +11911,16 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
+          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>90009650000</t>
+          <t>93519420000</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11936,12 +11931,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>93519420000</t>
+          <t>93519430000</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -11956,16 +11951,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>93519430000</t>
+          <t>93519440000</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11976,16 +11971,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>93519440000</t>
+          <t>93519460000</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11996,16 +11991,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>93519460000</t>
+          <t>93519540000</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12016,16 +12011,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
+          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>93519540000</t>
+          <t>93519470000</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12036,16 +12031,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>93519470000</t>
+          <t>93519500000</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12056,16 +12051,16 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>93519500000</t>
+          <t>93519550000</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12076,16 +12071,16 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>93519550000</t>
+          <t>93519510000</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12096,16 +12091,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>93519510000</t>
+          <t>93519490000</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12116,16 +12111,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>93519490000</t>
+          <t>93519530000</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12136,16 +12131,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>93519530000</t>
+          <t>93520160000</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12156,16 +12151,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>93520160000</t>
+          <t>93519400000</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12176,36 +12171,36 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>FHN BABY CAT 400GR · 90413910100</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>93519400000</t>
+          <t>90413910100</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>ROYAL CANIN</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FHN BABY CAT 400GR · 90413910100</t>
+          <t>FHN SENSIBLE 2KG · 90401470000</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>90413910100</t>
+          <t>90401470000</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12216,16 +12211,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FHN SENSIBLE 2KG · 90401470000</t>
+          <t>ROYAL CANIN CARDIAC 2KG · 93504700000</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>90401470000</t>
+          <t>93504700000</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12236,16 +12231,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ROYAL CANIN CARDIAC 2KG · 93504700000</t>
+          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>93504700000</t>
+          <t>93505490000</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12256,16 +12251,16 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
+          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>93505490000</t>
+          <t>90006770000</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12276,16 +12271,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
+          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>90006770000</t>
+          <t>93505710000</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12296,16 +12291,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
+          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>93505710000</t>
+          <t>93505700000</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12316,16 +12311,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
+          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>93505700000</t>
+          <t>93505510000</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12336,16 +12331,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
+          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>93505510000</t>
+          <t>90006780000</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12356,16 +12351,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+          <t>ROYAL CANIN MEDIUM PUPPY 1 KG · 90405320000</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>90006780000</t>
+          <t>90405320000</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12376,16 +12371,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ROYAL CANIN MEDIUM PUPPY 1 KG · 90405320000</t>
+          <t>ROYAL CANIN RENAL 2KG · 93510310000</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>90405320000</t>
+          <t>93510310000</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12396,16 +12391,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ROYAL CANIN RENAL 2KG · 93510310000</t>
+          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>93510310000</t>
+          <t>90006790000</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12416,12 +12411,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
+          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>90006790000</t>
+          <t>93505570000</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -12436,16 +12431,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>93505570000</t>
+          <t>90407030000</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12456,16 +12451,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
+          <t>ROYALCANIN SATIETY 1.5KG · 93516260000</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>90407030000</t>
+          <t>93516260000</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12476,12 +12471,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ROYALCANIN SATIETY 1.5KG · 93516260000</t>
+          <t>UC SNACK BARRA RELLENA M/MANI 1UD · 93513050000</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>93516260000</t>
+          <t>93513050000</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -12489,101 +12484,81 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ROYAL CANIN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA M/MANI 1UD · 93513050000</t>
+          <t>D WS POLLO Y ARROZ INTEGRAL 16L · 93500000229</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>93513050000</t>
+          <t>93500000229</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SUNSHINE MILLS</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>D WS POLLO Y ARROZ INTEGRAL 16L · 93500000229</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>93500000229</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SUNSHINE MILLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>93500000342</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>6</v>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
           <t>SUPERKAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>P&amp;G | HOSPITAL COSTA VERDE</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>P&amp;G | HOSPITAL COSTA VERDE</t>
-        </is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
           <t>Inventario al</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>21.10.2026</t>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
         </is>
       </c>
     </row>
